--- a/平均轉乘次數趨勢分析/花蓮縣月平均轉乘次數.xlsx
+++ b/平均轉乘次數趨勢分析/花蓮縣月平均轉乘次數.xlsx
@@ -482,7 +482,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>53632</v>
+        <v>53609</v>
       </c>
       <c r="C2" t="n">
         <v>2553</v>
@@ -494,7 +494,7 @@
         <v>256</v>
       </c>
       <c r="F2" t="n">
-        <v>45457</v>
+        <v>45434</v>
       </c>
       <c r="G2" t="n">
         <v>2297</v>
@@ -514,7 +514,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>47468</v>
+        <v>47458</v>
       </c>
       <c r="C3" t="n">
         <v>2267</v>
@@ -526,7 +526,7 @@
         <v>189</v>
       </c>
       <c r="F3" t="n">
-        <v>41113</v>
+        <v>41103</v>
       </c>
       <c r="G3" t="n">
         <v>2078</v>
@@ -546,7 +546,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>53421</v>
+        <v>53410</v>
       </c>
       <c r="C4" t="n">
         <v>2630</v>
@@ -558,7 +558,7 @@
         <v>232</v>
       </c>
       <c r="F4" t="n">
-        <v>46998</v>
+        <v>46987</v>
       </c>
       <c r="G4" t="n">
         <v>2398</v>
@@ -578,19 +578,19 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>66365</v>
+        <v>66353</v>
       </c>
       <c r="C5" t="n">
         <v>2675</v>
       </c>
       <c r="D5" t="n">
-        <v>11433</v>
+        <v>11432</v>
       </c>
       <c r="E5" t="n">
         <v>341</v>
       </c>
       <c r="F5" t="n">
-        <v>54932</v>
+        <v>54921</v>
       </c>
       <c r="G5" t="n">
         <v>2334</v>
@@ -610,19 +610,19 @@
         <v>14</v>
       </c>
       <c r="B6" t="n">
-        <v>61988</v>
+        <v>61973</v>
       </c>
       <c r="C6" t="n">
         <v>2535</v>
       </c>
       <c r="D6" t="n">
-        <v>11506</v>
+        <v>11505</v>
       </c>
       <c r="E6" t="n">
         <v>356</v>
       </c>
       <c r="F6" t="n">
-        <v>50482</v>
+        <v>50468</v>
       </c>
       <c r="G6" t="n">
         <v>2179</v>
@@ -642,22 +642,22 @@
         <v>15</v>
       </c>
       <c r="B7" t="n">
-        <v>70277</v>
+        <v>70245</v>
       </c>
       <c r="C7" t="n">
-        <v>2617</v>
+        <v>2614</v>
       </c>
       <c r="D7" t="n">
-        <v>12953</v>
+        <v>12950</v>
       </c>
       <c r="E7" t="n">
         <v>359</v>
       </c>
       <c r="F7" t="n">
-        <v>57324</v>
+        <v>57295</v>
       </c>
       <c r="G7" t="n">
-        <v>2258</v>
+        <v>2255</v>
       </c>
       <c r="H7" t="n">
         <v>0.037</v>
@@ -674,19 +674,19 @@
         <v>16</v>
       </c>
       <c r="B8" t="n">
-        <v>71113</v>
+        <v>71088</v>
       </c>
       <c r="C8" t="n">
         <v>2785</v>
       </c>
       <c r="D8" t="n">
-        <v>13577</v>
+        <v>13574</v>
       </c>
       <c r="E8" t="n">
         <v>391</v>
       </c>
       <c r="F8" t="n">
-        <v>57536</v>
+        <v>57514</v>
       </c>
       <c r="G8" t="n">
         <v>2394</v>
@@ -706,7 +706,7 @@
         <v>17</v>
       </c>
       <c r="B9" t="n">
-        <v>47727</v>
+        <v>47704</v>
       </c>
       <c r="C9" t="n">
         <v>1804</v>
@@ -718,7 +718,7 @@
         <v>172</v>
       </c>
       <c r="F9" t="n">
-        <v>39345</v>
+        <v>39322</v>
       </c>
       <c r="G9" t="n">
         <v>1632</v>
@@ -730,7 +730,7 @@
         <v>0.021</v>
       </c>
       <c r="J9" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="10">
@@ -738,7 +738,7 @@
         <v>18</v>
       </c>
       <c r="B10" t="n">
-        <v>47789</v>
+        <v>47769</v>
       </c>
       <c r="C10" t="n">
         <v>1867</v>
@@ -750,7 +750,7 @@
         <v>264</v>
       </c>
       <c r="F10" t="n">
-        <v>37503</v>
+        <v>37483</v>
       </c>
       <c r="G10" t="n">
         <v>1603</v>
@@ -770,7 +770,7 @@
         <v>19</v>
       </c>
       <c r="B11" t="n">
-        <v>61495</v>
+        <v>61483</v>
       </c>
       <c r="C11" t="n">
         <v>2314</v>
@@ -782,7 +782,7 @@
         <v>363</v>
       </c>
       <c r="F11" t="n">
-        <v>45945</v>
+        <v>45933</v>
       </c>
       <c r="G11" t="n">
         <v>1951</v>
@@ -802,19 +802,19 @@
         <v>20</v>
       </c>
       <c r="B12" t="n">
-        <v>62031</v>
+        <v>61968</v>
       </c>
       <c r="C12" t="n">
         <v>2459</v>
       </c>
       <c r="D12" t="n">
-        <v>14190</v>
+        <v>14181</v>
       </c>
       <c r="E12" t="n">
         <v>315</v>
       </c>
       <c r="F12" t="n">
-        <v>47841</v>
+        <v>47787</v>
       </c>
       <c r="G12" t="n">
         <v>2144</v>
@@ -834,25 +834,25 @@
         <v>21</v>
       </c>
       <c r="B13" t="n">
-        <v>60184</v>
+        <v>60155</v>
       </c>
       <c r="C13" t="n">
         <v>2557</v>
       </c>
       <c r="D13" t="n">
-        <v>14978</v>
+        <v>14971</v>
       </c>
       <c r="E13" t="n">
         <v>423</v>
       </c>
       <c r="F13" t="n">
-        <v>45206</v>
+        <v>45184</v>
       </c>
       <c r="G13" t="n">
         <v>2134</v>
       </c>
       <c r="H13" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="I13" t="n">
         <v>0.028</v>
@@ -866,19 +866,19 @@
         <v>22</v>
       </c>
       <c r="B14" t="n">
-        <v>56418</v>
+        <v>56400</v>
       </c>
       <c r="C14" t="n">
         <v>2504</v>
       </c>
       <c r="D14" t="n">
-        <v>12637</v>
+        <v>12635</v>
       </c>
       <c r="E14" t="n">
         <v>304</v>
       </c>
       <c r="F14" t="n">
-        <v>43781</v>
+        <v>43765</v>
       </c>
       <c r="G14" t="n">
         <v>2200</v>
@@ -898,19 +898,19 @@
         <v>23</v>
       </c>
       <c r="B15" t="n">
-        <v>49235</v>
+        <v>49208</v>
       </c>
       <c r="C15" t="n">
         <v>2247</v>
       </c>
       <c r="D15" t="n">
-        <v>9085</v>
+        <v>9084</v>
       </c>
       <c r="E15" t="n">
         <v>319</v>
       </c>
       <c r="F15" t="n">
-        <v>40150</v>
+        <v>40124</v>
       </c>
       <c r="G15" t="n">
         <v>1928</v>
@@ -930,7 +930,7 @@
         <v>24</v>
       </c>
       <c r="B16" t="n">
-        <v>52671</v>
+        <v>52652</v>
       </c>
       <c r="C16" t="n">
         <v>2429</v>
@@ -942,7 +942,7 @@
         <v>270</v>
       </c>
       <c r="F16" t="n">
-        <v>43468</v>
+        <v>43449</v>
       </c>
       <c r="G16" t="n">
         <v>2159</v>
@@ -962,7 +962,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="n">
-        <v>65166</v>
+        <v>65149</v>
       </c>
       <c r="C17" t="n">
         <v>2585</v>
@@ -974,7 +974,7 @@
         <v>425</v>
       </c>
       <c r="F17" t="n">
-        <v>46480</v>
+        <v>46463</v>
       </c>
       <c r="G17" t="n">
         <v>2160</v>
@@ -994,19 +994,19 @@
         <v>26</v>
       </c>
       <c r="B18" t="n">
-        <v>67288</v>
+        <v>67260</v>
       </c>
       <c r="C18" t="n">
         <v>2446</v>
       </c>
       <c r="D18" t="n">
-        <v>20558</v>
+        <v>20557</v>
       </c>
       <c r="E18" t="n">
         <v>406</v>
       </c>
       <c r="F18" t="n">
-        <v>46730</v>
+        <v>46703</v>
       </c>
       <c r="G18" t="n">
         <v>2040</v>
@@ -1026,19 +1026,19 @@
         <v>27</v>
       </c>
       <c r="B19" t="n">
-        <v>53501</v>
+        <v>53476</v>
       </c>
       <c r="C19" t="n">
         <v>2314</v>
       </c>
       <c r="D19" t="n">
-        <v>15753</v>
+        <v>15752</v>
       </c>
       <c r="E19" t="n">
         <v>408</v>
       </c>
       <c r="F19" t="n">
-        <v>37748</v>
+        <v>37724</v>
       </c>
       <c r="G19" t="n">
         <v>1906</v>
@@ -1050,7 +1050,7 @@
         <v>0.026</v>
       </c>
       <c r="J19" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="20">
@@ -1058,7 +1058,7 @@
         <v>28</v>
       </c>
       <c r="B20" t="n">
-        <v>61964</v>
+        <v>61935</v>
       </c>
       <c r="C20" t="n">
         <v>2670</v>
@@ -1070,7 +1070,7 @@
         <v>408</v>
       </c>
       <c r="F20" t="n">
-        <v>43962</v>
+        <v>43933</v>
       </c>
       <c r="G20" t="n">
         <v>2262</v>
@@ -1090,7 +1090,7 @@
         <v>29</v>
       </c>
       <c r="B21" t="n">
-        <v>49552</v>
+        <v>49529</v>
       </c>
       <c r="C21" t="n">
         <v>2586</v>
@@ -1102,7 +1102,7 @@
         <v>422</v>
       </c>
       <c r="F21" t="n">
-        <v>36975</v>
+        <v>36952</v>
       </c>
       <c r="G21" t="n">
         <v>2164</v>
@@ -1122,7 +1122,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>46265</v>
+        <v>46248</v>
       </c>
       <c r="C22" t="n">
         <v>2136</v>
@@ -1134,7 +1134,7 @@
         <v>255</v>
       </c>
       <c r="F22" t="n">
-        <v>37778</v>
+        <v>37761</v>
       </c>
       <c r="G22" t="n">
         <v>1881</v>
@@ -1154,22 +1154,22 @@
         <v>31</v>
       </c>
       <c r="B23" t="n">
-        <v>64114</v>
+        <v>62941</v>
       </c>
       <c r="C23" t="n">
-        <v>2603</v>
+        <v>2574</v>
       </c>
       <c r="D23" t="n">
-        <v>18538</v>
+        <v>18292</v>
       </c>
       <c r="E23" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F23" t="n">
-        <v>45576</v>
+        <v>44649</v>
       </c>
       <c r="G23" t="n">
-        <v>2189</v>
+        <v>2163</v>
       </c>
       <c r="H23" t="n">
         <v>0.041</v>
@@ -1186,31 +1186,31 @@
         <v>32</v>
       </c>
       <c r="B24" t="n">
-        <v>76529</v>
+        <v>48451</v>
       </c>
       <c r="C24" t="n">
-        <v>3403</v>
+        <v>2109</v>
       </c>
       <c r="D24" t="n">
-        <v>15933</v>
+        <v>10296</v>
       </c>
       <c r="E24" t="n">
-        <v>393</v>
+        <v>231</v>
       </c>
       <c r="F24" t="n">
-        <v>60596</v>
+        <v>38155</v>
       </c>
       <c r="G24" t="n">
-        <v>3010</v>
+        <v>1878</v>
       </c>
       <c r="H24" t="n">
         <v>0.044</v>
       </c>
       <c r="I24" t="n">
-        <v>0.025</v>
+        <v>0.022</v>
       </c>
       <c r="J24" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="25">
@@ -1218,31 +1218,31 @@
         <v>33</v>
       </c>
       <c r="B25" t="n">
-        <v>42489</v>
+        <v>41526</v>
       </c>
       <c r="C25" t="n">
-        <v>2099</v>
+        <v>2078</v>
       </c>
       <c r="D25" t="n">
-        <v>8564</v>
+        <v>8348</v>
       </c>
       <c r="E25" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F25" t="n">
-        <v>33925</v>
+        <v>33178</v>
       </c>
       <c r="G25" t="n">
-        <v>1862</v>
+        <v>1842</v>
       </c>
       <c r="H25" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="I25" t="n">
         <v>0.028</v>
       </c>
       <c r="J25" t="n">
-        <v>0.055</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="26">
@@ -1250,22 +1250,22 @@
         <v>34</v>
       </c>
       <c r="B26" t="n">
-        <v>39185</v>
+        <v>38906</v>
       </c>
       <c r="C26" t="n">
-        <v>2041</v>
+        <v>2038</v>
       </c>
       <c r="D26" t="n">
-        <v>7872</v>
+        <v>7785</v>
       </c>
       <c r="E26" t="n">
         <v>257</v>
       </c>
       <c r="F26" t="n">
-        <v>31313</v>
+        <v>31121</v>
       </c>
       <c r="G26" t="n">
-        <v>1784</v>
+        <v>1781</v>
       </c>
       <c r="H26" t="n">
         <v>0.052</v>
